--- a/output/pdf_financials_xlsx/B.xlsx
+++ b/output/pdf_financials_xlsx/B.xlsx
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.165515</v>
+        <v>-0.165515</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.149731</v>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.165515</v>
+        <v>-0.165515</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.149731</v>
@@ -6306,37 +6306,37 @@
         <v>1.040038</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.040038</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.389778</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.389778</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.550276</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.522893</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.532137</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.151557</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.313905</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.452118</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.4718</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.446775</v>
       </c>
     </row>
     <row r="93">
@@ -10117,7 +10117,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -22703,7 +22707,7 @@
         </is>
       </c>
       <c r="I140" s="5" t="n">
-        <v>0.165515</v>
+        <v>-0.165515</v>
       </c>
       <c r="J140" s="5" t="n">
         <v>-0.149731</v>

--- a/output/pdf_financials_xlsx/B.xlsx
+++ b/output/pdf_financials_xlsx/B.xlsx
@@ -1113,19 +1113,19 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-9.1e-05</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00015</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000128</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00013</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000116</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.000409</v>
       </c>
     </row>
     <row r="13">
@@ -2179,19 +2179,19 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.211637</v>
+        <v>0.211728</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.152</v>
+        <v>-0.15185</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.172491</v>
+        <v>-0.172363</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.548551</v>
+        <v>-0.548421</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.181256</v>
+        <v>-0.18114</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.40574</v>
@@ -2215,7 +2215,7 @@
         <v>-0.421005</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.45922</v>
+        <v>-0.459629</v>
       </c>
     </row>
     <row r="28">
@@ -2311,19 +2311,19 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.211637</v>
+        <v>0.211728</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.152</v>
+        <v>-0.15185</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.172491</v>
+        <v>-0.172363</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.548551</v>
+        <v>-0.548421</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.181256</v>
+        <v>-0.18114</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.40574</v>
@@ -2347,7 +2347,7 @@
         <v>-0.421005</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.45922</v>
+        <v>-0.459629</v>
       </c>
     </row>
     <row r="30">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -24871,7 +24871,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">

--- a/output/pdf_financials_xlsx/B.xlsx
+++ b/output/pdf_financials_xlsx/B.xlsx
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.001931</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.001356</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.211728</v>
+        <v>0.213659</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.15185</v>
+        <v>-0.150494</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.172363</v>
@@ -6837,43 +6837,43 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.062457</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.001451</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.000333</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003655</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>0.003201</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002564</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001933</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001288</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001502</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004974</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>-0.018381</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>0.028613</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005008</v>
       </c>
     </row>
     <row r="102">
@@ -7167,43 +7167,43 @@
         </is>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.041132</v>
+        <v>0.021325</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.090679</v>
+        <v>0.09213</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.131733</v>
+        <v>0.132066</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.012236</v>
+        <v>-0.015891</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.022244</v>
+        <v>0.025445</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.103231</v>
+        <v>0.100667</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.07456400000000001</v>
+        <v>0.072631</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.048122</v>
+        <v>0.046834</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>-0.469069</v>
+        <v>-0.470571</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.106553</v>
+        <v>0.101579</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>1.25459</v>
+        <v>1.236209</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.256366</v>
+        <v>0.284979</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>-0.281705</v>
+        <v>-0.286713</v>
       </c>
     </row>
     <row r="107">
@@ -9161,7 +9161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U173"/>
+  <dimension ref="A1:U176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13348,7 +13348,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -18878,7 +18882,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -19688,7 +19696,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -20090,7 +20102,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -25166,7 +25182,11 @@
           <t>Amortization expense $</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -26058,6 +26078,303 @@
         </is>
       </c>
       <c r="U173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>outstanding                                                   15,275,511        13,368,662</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>$ (51,960) 314,232 220,000 (1,025) Total 4,337,250 1,200,000 (541,187)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>5.29387</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>-0.18344</v>
+      </c>
+      <c r="H174" s="5" t="n">
+        <v>5.258335</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>outstanding                                                   15,275,511        13,368,662</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>outstanding                                                   15,275,511        13,368,662 total</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>outstanding                                                   15,275,511        13,368,662</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>$ (541,187) (183,440) Deficit</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>-2.728535</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>-2.545095</v>
+      </c>
+      <c r="H176" s="5" t="n">
+        <v>-2.003908</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
